--- a/Envíos/Operativa_Grupo5_12032026.xlsx
+++ b/Envíos/Operativa_Grupo5_12032026.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupoanalistas-my.sharepoint.com/personal/jpuerta_afi_es/Documents/Documentos/Master Quant/Gestión de activos/Trabajo gestión cuantitativa/Trabajo_gestion_cuantitativa/Envíos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F623CEDB-3327-4B0A-8E02-8998F4DBB3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{790360EF-04C4-4BDF-8F8C-DCA999DAE56E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Operativa" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" calcOnSave="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -155,7 +155,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -425,286 +425,301 @@
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="3">
         <v>564</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="3">
         <v>1180.40002441406</v>
       </c>
-      <c r="D2" s="2">
-        <v>1.1803999999999999</v>
-      </c>
-      <c r="E2" s="2">
-        <v>1181.5804000000001</v>
+      <c r="D2" s="3">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="E2" s="3">
+        <f t="shared" ref="E2:E17" si="0">C2*(1+D2)</f>
+        <v>1180.9902244262669</v>
       </c>
       <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
+      <c r="G2" s="3"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="3">
         <v>4362</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="3">
         <v>152.64999389648401</v>
       </c>
-      <c r="D3" s="2">
-        <v>0.15260000000000001</v>
-      </c>
-      <c r="E3" s="2">
-        <v>152.80260000000001</v>
+      <c r="D3" s="3">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="E3" s="3">
+        <f t="shared" si="0"/>
+        <v>152.72631889343225</v>
       </c>
       <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
+      <c r="G3" s="3"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="3">
         <v>36623</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="3">
         <v>18.184999465942301</v>
       </c>
-      <c r="D4" s="2">
-        <v>1.8200000000000001E-2</v>
-      </c>
-      <c r="E4" s="2">
-        <v>18.203199999999999</v>
+      <c r="D4" s="3">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="E4" s="3">
+        <f t="shared" si="0"/>
+        <v>18.19409196567527</v>
       </c>
       <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
+      <c r="G4" s="3"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="3">
         <v>4716</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="3">
         <v>141.19999694824199</v>
       </c>
-      <c r="D5" s="2">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="E5" s="2">
-        <v>141.34119999999999</v>
+      <c r="D5" s="3">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="E5" s="3">
+        <f t="shared" si="0"/>
+        <v>141.2705969467161</v>
       </c>
       <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
+      <c r="G5" s="3"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="3">
         <v>14659</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="3">
         <v>45.430000305175703</v>
       </c>
-      <c r="D6" s="2">
-        <v>4.5400000000000003E-2</v>
-      </c>
-      <c r="E6" s="2">
-        <v>45.4754</v>
+      <c r="D6" s="3">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="E6" s="3">
+        <f t="shared" si="0"/>
+        <v>45.45271530532829</v>
       </c>
       <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
+      <c r="G6" s="3"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="3">
         <v>3987</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="3">
         <v>167.02000427246</v>
       </c>
-      <c r="D7" s="2">
-        <v>0.16700000000000001</v>
-      </c>
-      <c r="E7" s="2">
-        <v>167.18700000000001</v>
+      <c r="D7" s="3">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="E7" s="3">
+        <f t="shared" si="0"/>
+        <v>167.10351427459622</v>
       </c>
       <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
+      <c r="G7" s="3"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="3">
         <v>3159</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="3">
         <v>210.80000305175699</v>
       </c>
-      <c r="D8" s="2">
-        <v>0.21079999999999999</v>
-      </c>
-      <c r="E8" s="2">
-        <v>211.01079999999999</v>
+      <c r="D8" s="3">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="E8" s="3">
+        <f t="shared" si="0"/>
+        <v>210.90540305328287</v>
       </c>
       <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
+      <c r="G8" s="3"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="3">
         <v>2276</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="3">
         <v>292.600006103515</v>
       </c>
-      <c r="D9" s="2">
-        <v>0.29260000000000003</v>
-      </c>
-      <c r="E9" s="2">
-        <v>292.89260000000002</v>
+      <c r="D9" s="3">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="E9" s="3">
+        <f t="shared" si="0"/>
+        <v>292.74630610656675</v>
       </c>
       <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
+      <c r="G9" s="3"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>13</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="3">
         <v>9919</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="3">
         <v>67.139999389648395</v>
       </c>
-      <c r="D10" s="2">
-        <v>6.7100000000000007E-2</v>
-      </c>
-      <c r="E10" s="2">
-        <v>67.207099999999997</v>
+      <c r="D10" s="3">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="E10" s="3">
+        <f t="shared" si="0"/>
+        <v>67.173569389343214</v>
       </c>
       <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
+      <c r="G10" s="3"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>14</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="3">
         <v>17020</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="3">
         <v>39.130001068115199</v>
       </c>
-      <c r="D11" s="2">
-        <v>3.9100000000000003E-2</v>
-      </c>
-      <c r="E11" s="2">
-        <v>39.1691</v>
+      <c r="D11" s="3">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="E11" s="3">
+        <f t="shared" si="0"/>
+        <v>39.149566068649257</v>
       </c>
       <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
+      <c r="G11" s="3"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>15</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="3">
         <v>726</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="3">
         <v>917.29998779296795</v>
       </c>
-      <c r="D12" s="2">
-        <v>0.9173</v>
-      </c>
-      <c r="E12" s="2">
-        <v>918.21730000000002</v>
+      <c r="D12" s="3">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="E12" s="3">
+        <f t="shared" si="0"/>
+        <v>917.75863778686437</v>
       </c>
       <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
+      <c r="G12" s="3"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>16</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="3">
         <v>25909</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="3">
         <v>25.704999923706001</v>
       </c>
-      <c r="D13" s="2">
-        <v>2.5700000000000001E-2</v>
-      </c>
-      <c r="E13" s="2">
-        <v>25.730699999999999</v>
+      <c r="D13" s="3">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="E13" s="3">
+        <f t="shared" si="0"/>
+        <v>25.717852423667853</v>
       </c>
       <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
+      <c r="G13" s="3"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>17</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="3">
         <v>429</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="3">
         <v>1550.5</v>
       </c>
-      <c r="D14" s="2">
-        <v>1.5505</v>
-      </c>
-      <c r="E14" s="2">
-        <v>1552.0505000000001</v>
+      <c r="D14" s="3">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="E14" s="3">
+        <f t="shared" si="0"/>
+        <v>1551.2752499999999</v>
       </c>
       <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
+      <c r="G14" s="3"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>18</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="3">
         <v>1081</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="3">
         <v>616</v>
       </c>
-      <c r="D15" s="2">
-        <v>0.61599999999999999</v>
-      </c>
-      <c r="E15" s="2">
-        <v>616.61599999999999</v>
+      <c r="D15" s="3">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="E15" s="3">
+        <f t="shared" si="0"/>
+        <v>616.30799999999999</v>
       </c>
       <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
+      <c r="G15" s="3"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>19</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="3">
         <v>3871</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="3">
         <v>172.03999328613199</v>
       </c>
-      <c r="D16" s="2">
-        <v>0.17199999999999999</v>
-      </c>
-      <c r="E16" s="2">
-        <v>172.21199999999999</v>
+      <c r="D16" s="3">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="E16" s="3">
+        <f t="shared" si="0"/>
+        <v>172.12601328277503</v>
       </c>
       <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
+      <c r="G16" s="3"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
@@ -713,17 +728,18 @@
       <c r="B17" s="3">
         <v>366.96075312617717</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="3">
         <v>5.0297000000000001</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="3">
         <v>0</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" s="3">
+        <f t="shared" si="0"/>
         <v>5.0297000000000001</v>
       </c>
       <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
+      <c r="G17" s="3"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C18" s="2"/>
